--- a/jpcore-r4/feature/swg2_servicerequest/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/ValueSet-jp-condition-disease-outcome-hl70241-jhsd0006-vs.xlsx
@@ -94,7 +94,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>copyright HL7 Japan (出典：HL7-0241)
+    <t>Copyright HL7 Japan (出典：HL7-0241)
 Copyright Japanese  Association of Healthcare Information Systems Industry(JAHIS)  一般社団法人保健医療福祉情報システム工業会</t>
   </si>
   <si>
